--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times_success.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times_success.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001413777489215136</v>
+        <v>0.001106218436034396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001248221597634256</v>
+        <v>0.0009810000425204634</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001710138238267973</v>
+        <v>0.001347329046111554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007148866372881457</v>
+        <v>0.0004556673974730075</v>
       </c>
       <c r="F2" t="n">
-        <v>2.803020060956478</v>
+        <v>1.614744230508804</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001373968267580494</v>
+        <v>0.001092969119781628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00123238914005924</v>
+        <v>0.0009552891622297466</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001705298374872655</v>
+        <v>0.001295143453171477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006427092012017965</v>
+        <v>0.0004336674755904824</v>
       </c>
       <c r="F3" t="n">
-        <v>2.820337651073933</v>
+        <v>1.713407080620527</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001447882417123765</v>
+        <v>0.001040253333048895</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001352224949514493</v>
+        <v>0.0009203008422628045</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001806899911025539</v>
+        <v>0.001246879891259596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005995707743568346</v>
+        <v>0.0004231457808054984</v>
       </c>
       <c r="F4" t="n">
-        <v>2.987753646224737</v>
+        <v>1.765146588534117</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00153689750470221</v>
+        <v>0.001108634173870087</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001380711700767279</v>
+        <v>0.001001142540480941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001981522452551872</v>
+        <v>0.001381535727996379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007882616756251082</v>
+        <v>0.0004698191792704165</v>
       </c>
       <c r="F5" t="n">
-        <v>3.111202481240034</v>
+        <v>1.875252706259489</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001515016602352261</v>
+        <v>0.00113381422823295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001408079973771237</v>
+        <v>0.0009819191845599562</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001937737480038777</v>
+        <v>0.001349262516014278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006115041533485055</v>
+        <v>0.0004366758570540696</v>
       </c>
       <c r="F6" t="n">
-        <v>3.186009917408228</v>
+        <v>1.916745700836182</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001618054184364155</v>
+        <v>0.001383686736226082</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001495189157431014</v>
+        <v>0.001192044283961877</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002034439947456121</v>
+        <v>0.001745447486173362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008357342390809208</v>
+        <v>0.0005238524626474827</v>
       </c>
       <c r="F7" t="n">
-        <v>3.433950301259756</v>
+        <v>2.069817410707474</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001703794156201184</v>
+        <v>0.001286541622830555</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001481279251165688</v>
+        <v>0.001062899131793529</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002172171670245007</v>
+        <v>0.00149103406118229</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007085426151752472</v>
+        <v>0.0004619891790207476</v>
       </c>
       <c r="F8" t="n">
-        <v>3.449571636468172</v>
+        <v>2.146564075499773</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001685048204381019</v>
+        <v>0.003093309862306342</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001607514187926427</v>
+        <v>0.002349184243939817</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002136508282274008</v>
+        <v>0.008274883250705897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005970175773836673</v>
+        <v>0.0004741514092121197</v>
       </c>
       <c r="F9" t="n">
-        <v>3.541561101078987</v>
+        <v>2.315141533762217</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00173310502897948</v>
+        <v>0.001784052501898259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001608933351235464</v>
+        <v>0.00165872170124203</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002080455797258764</v>
+        <v>0.004232314028777182</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006557850271929056</v>
+        <v>0.0005085671876500151</v>
       </c>
       <c r="F10" t="n">
-        <v>3.664311307370663</v>
+        <v>2.338768331557512</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002673905896954239</v>
+        <v>0.00216375493328087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002425237527349964</v>
+        <v>0.002839954264927655</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004512070778291672</v>
+        <v>0.01338846884784289</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0006266054156835058</v>
+        <v>0.0004540572748131429</v>
       </c>
       <c r="F11" t="n">
-        <v>3.760652349144221</v>
+        <v>2.578810232579708</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003538795851636678</v>
+        <v>0.00821673404192552</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003872359180240892</v>
+        <v>0.02497066914918833</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004392845036927611</v>
+        <v>0.006666090012746578</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000575122340493142</v>
+        <v>0.0004564268204073111</v>
       </c>
       <c r="F12" t="n">
-        <v>3.99679329380393</v>
+        <v>2.766005976498127</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006770376580534503</v>
+        <v>0.005802852406632155</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008250817622756585</v>
+        <v>0.007977541686268524</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004082048421259969</v>
+        <v>0.007837912319608184</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0007355269089910305</v>
+        <v>0.0004458546371585349</v>
       </c>
       <c r="F13" t="n">
-        <v>4.327445442378521</v>
+        <v>3.069787151366472</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009630310017964803</v>
+        <v>0.009155482960133148</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01281959409883712</v>
+        <v>0.01512118171643922</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007634900466358403</v>
+        <v>0.006432313375019779</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0005356005595985618</v>
+        <v>0.0004353835590732977</v>
       </c>
       <c r="F14" t="n">
-        <v>4.719483923316002</v>
+        <v>3.528094295710325</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01299020395096277</v>
+        <v>0.0172469839845708</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01464112331301962</v>
+        <v>0.02510080688718554</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01028498397902288</v>
+        <v>0.01262973328509058</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0006597029442230287</v>
+        <v>0.0005146774795970747</v>
       </c>
       <c r="F15" t="n">
-        <v>5.269692835911196</v>
+        <v>3.741449304381195</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0368121403735131</v>
+        <v>0.03642006181932326</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03803977508141543</v>
+        <v>0.03936962039248707</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01156743097817525</v>
+        <v>0.0113399744308977</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0006129711162595248</v>
+        <v>0.0005114826508947919</v>
       </c>
       <c r="F16" t="n">
-        <v>5.564049435469012</v>
+        <v>4.273121611044115</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02399068793359523</v>
+        <v>0.0329587259898703</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02667937145193314</v>
+        <v>0.06034088955361354</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008647560589121316</v>
+        <v>0.01193659446804171</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000602119681124966</v>
+        <v>0.0005516898150003895</v>
       </c>
       <c r="F17" t="n">
-        <v>5.584978164898025</v>
+        <v>4.237305115494463</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06135642322677574</v>
+        <v>0.06529431295071152</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06530732538965645</v>
+        <v>0.05786276718306287</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006782259590601405</v>
+        <v>0.02052533568187048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0005101986887614027</v>
+        <v>0.0005077481011698103</v>
       </c>
       <c r="F18" t="n">
-        <v>5.55282209671679</v>
+        <v>4.204975934569226</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0761898273948389</v>
+        <v>0.09018855823328854</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07847470850146447</v>
+        <v>0.1153381205527694</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01125116112037889</v>
+        <v>0.02260496783674171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0005777044637149877</v>
+        <v>0.0004433293070178479</v>
       </c>
       <c r="F19" t="n">
-        <v>5.775698809287487</v>
+        <v>4.797869182396226</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1104094070194858</v>
+        <v>0.1241222477701464</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1589494243509964</v>
+        <v>0.1092241268435662</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007576395164153749</v>
+        <v>0.02497960475739092</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0007936096256966458</v>
+        <v>0.0004923957998731307</v>
       </c>
       <c r="F20" t="n">
-        <v>5.965274144791895</v>
+        <v>5.626818424419445</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1177150776687389</v>
+        <v>0.1147536468946513</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1224871545246887</v>
+        <v>0.1191699651664951</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01555701622363323</v>
+        <v>0.02908638842304104</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000746175430582038</v>
+        <v>0.0005153220951218497</v>
       </c>
       <c r="F21" t="n">
-        <v>6.843084735028884</v>
+        <v>5.869560523756912</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times_success.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times_success.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001106218436034396</v>
+        <v>0.001099896678933874</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009810000425204634</v>
+        <v>0.0009372807131148874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001347329046111554</v>
+        <v>0.00121252330369316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004556673974730075</v>
+        <v>0.0003898808604571968</v>
       </c>
       <c r="F2" t="n">
-        <v>1.614744230508804</v>
+        <v>0.5709892903268338</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001092969119781628</v>
+        <v>0.001198643443640321</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009552891622297466</v>
+        <v>0.001041068398626521</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001295143453171477</v>
+        <v>0.00151529737515375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004336674755904824</v>
+        <v>0.0004215190815739333</v>
       </c>
       <c r="F3" t="n">
-        <v>1.713407080620527</v>
+        <v>0.6259903608262539</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001040253333048895</v>
+        <v>0.001254161630058661</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009203008422628045</v>
+        <v>0.001110290721990168</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001246879891259596</v>
+        <v>0.001492769143078476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004231457808054984</v>
+        <v>0.0005129258113447577</v>
       </c>
       <c r="F4" t="n">
-        <v>1.765146588534117</v>
+        <v>0.6294843511283398</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001108634173870087</v>
+        <v>0.001197830853052437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001001142540480941</v>
+        <v>0.00105851917527616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001381535727996379</v>
+        <v>0.001431979954941198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004698191792704165</v>
+        <v>0.0004535508959088474</v>
       </c>
       <c r="F5" t="n">
-        <v>1.875252706259489</v>
+        <v>0.6433845806121826</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00113381422823295</v>
+        <v>0.001250870805233717</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009819191845599562</v>
+        <v>0.001112818325636909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001349262516014278</v>
+        <v>0.001479770840378478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004366758570540696</v>
+        <v>0.0004605699214152992</v>
       </c>
       <c r="F6" t="n">
-        <v>1.916745700836182</v>
+        <v>0.746490034610033</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001383686736226082</v>
+        <v>0.00133532419684343</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001192044283961877</v>
+        <v>0.001250666765263304</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001745447486173362</v>
+        <v>0.001700286722043529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005238524626474827</v>
+        <v>0.0005404108599759639</v>
       </c>
       <c r="F7" t="n">
-        <v>2.069817410707474</v>
+        <v>0.8117360903322697</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001286541622830555</v>
+        <v>0.001676240055821836</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001062899131793529</v>
+        <v>0.001795003336155787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00149103406118229</v>
+        <v>0.001983577546197921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004619891790207476</v>
+        <v>0.0004581291470866726</v>
       </c>
       <c r="F8" t="n">
-        <v>2.146564075499773</v>
+        <v>1.128321632444859</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003093309862306342</v>
+        <v>0.001654027493204922</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002349184243939817</v>
+        <v>0.001895915016066283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008274883250705897</v>
+        <v>0.002114666613051668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004741514092121197</v>
+        <v>0.0004764047014165898</v>
       </c>
       <c r="F9" t="n">
-        <v>2.315141533762217</v>
+        <v>1.286375274509191</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001784052501898259</v>
+        <v>0.00198485744302161</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00165872170124203</v>
+        <v>0.00257868166663684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004232314028777182</v>
+        <v>0.001627084973733872</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0005085671876500151</v>
+        <v>0.0004837756760993061</v>
       </c>
       <c r="F10" t="n">
-        <v>2.338768331557512</v>
+        <v>1.398834803849459</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00216375493328087</v>
+        <v>0.002838161722756922</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002839954264927655</v>
+        <v>0.003371764967450872</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01338846884784289</v>
+        <v>0.002052275846945122</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004540572748131429</v>
+        <v>0.0004100923504903103</v>
       </c>
       <c r="F11" t="n">
-        <v>2.578810232579708</v>
+        <v>1.630984642058611</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00821673404192552</v>
+        <v>0.003556827605934813</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02497066914918833</v>
+        <v>0.004927404162008315</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006666090012746578</v>
+        <v>0.002047947204044583</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004564268204073111</v>
+        <v>0.0005361935822293162</v>
       </c>
       <c r="F12" t="n">
-        <v>2.766005976498127</v>
+        <v>1.976193261444569</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.005802852406632155</v>
+        <v>0.00868806738872081</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007977541686268524</v>
+        <v>0.01158929589320905</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007837912319608184</v>
+        <v>0.003374689174961532</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0004458546371585349</v>
+        <v>0.0004762852286848311</v>
       </c>
       <c r="F13" t="n">
-        <v>3.069787151366472</v>
+        <v>2.342407350838184</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009155482960133148</v>
+        <v>0.01356990537412154</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01512118171643922</v>
+        <v>0.01717038956121542</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006432313375019779</v>
+        <v>0.009431299114468224</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004353835590732977</v>
+        <v>0.0004670194703066954</v>
       </c>
       <c r="F14" t="n">
-        <v>3.528094295710325</v>
+        <v>2.686213685237631</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0172469839845708</v>
+        <v>0.01526325441738392</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02510080688718554</v>
+        <v>0.01700980540989165</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01262973328509058</v>
+        <v>0.01052809645956255</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005146774795970747</v>
+        <v>0.0004114445007871837</v>
       </c>
       <c r="F15" t="n">
-        <v>3.741449304381195</v>
+        <v>3.171708570638051</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03642006181932326</v>
+        <v>0.02263501526024985</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03936962039248707</v>
+        <v>0.02963591284896346</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0113399744308977</v>
+        <v>0.01997008479832272</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0005114826508947919</v>
+        <v>0.0004824899113737046</v>
       </c>
       <c r="F16" t="n">
-        <v>4.273121611044115</v>
+        <v>3.375714127846221</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0329587259898703</v>
+        <v>0.04032126564098606</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06034088955361354</v>
+        <v>0.04705814309735698</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01193659446804171</v>
+        <v>0.0171740292335508</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0005516898150003895</v>
+        <v>0.0004960207996191456</v>
       </c>
       <c r="F17" t="n">
-        <v>4.237305115494463</v>
+        <v>3.722370247802009</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06529431295071152</v>
+        <v>0.06084318640970219</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05786276718306287</v>
+        <v>0.1017765702115587</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02052533568187048</v>
+        <v>0.009667621343396604</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0005077481011698103</v>
+        <v>0.0004604104033205658</v>
       </c>
       <c r="F18" t="n">
-        <v>4.204975934569226</v>
+        <v>4.581387090750716</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09018855823328854</v>
+        <v>0.07643119469705401</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1153381205527694</v>
+        <v>0.08216716122276718</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02260496783674171</v>
+        <v>0.0204488707628722</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0004433293070178479</v>
+        <v>0.0004659322439692914</v>
       </c>
       <c r="F19" t="n">
-        <v>4.797869182396226</v>
+        <v>4.770013074537641</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1241222477701464</v>
+        <v>0.2125550920215075</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1092241268435662</v>
+        <v>0.2231357541295438</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02497960475739092</v>
+        <v>0.01545630763506605</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0004923957998731307</v>
+        <v>0.0004796131480751293</v>
       </c>
       <c r="F20" t="n">
-        <v>5.626818424419445</v>
+        <v>5.471774436314316</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1147536468946513</v>
+        <v>0.1532069665820176</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1191699651664951</v>
+        <v>0.1200528143849426</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02908638842304104</v>
+        <v>0.03094078486730509</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0005153220951218497</v>
+        <v>0.000505027836576725</v>
       </c>
       <c r="F21" t="n">
-        <v>5.869560523756912</v>
+        <v>6.238581290325294</v>
       </c>
     </row>
   </sheetData>
